--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K604"/>
+  <dimension ref="A1:K607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23984,6 +23984,123 @@
         <v>361.62</v>
       </c>
       <c r="K604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>352.67</v>
+      </c>
+      <c r="C605" t="n">
+        <v>351.76</v>
+      </c>
+      <c r="D605" t="n">
+        <v>361.09</v>
+      </c>
+      <c r="E605" t="n">
+        <v>365.07</v>
+      </c>
+      <c r="F605" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="G605" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="H605" t="n">
+        <v>348.68</v>
+      </c>
+      <c r="I605" t="n">
+        <v>354.35</v>
+      </c>
+      <c r="J605" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="C606" t="n">
+        <v>351.73</v>
+      </c>
+      <c r="D606" t="n">
+        <v>362.32</v>
+      </c>
+      <c r="E606" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="F606" t="n">
+        <v>361.78</v>
+      </c>
+      <c r="G606" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="H606" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="I606" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="J606" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>353.84</v>
+      </c>
+      <c r="C607" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="D607" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="E607" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="F607" t="n">
+        <v>361.84</v>
+      </c>
+      <c r="G607" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="H607" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="I607" t="n">
+        <v>355.39</v>
+      </c>
+      <c r="J607" t="n">
+        <v>362.56</v>
+      </c>
+      <c r="K607" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24000,7 +24117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B712"/>
+  <dimension ref="A1:B715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31123,6 +31240,36 @@
       </c>
       <c r="B712" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -31291,28 +31438,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1864274556990391</v>
+        <v>-0.1879042830050256</v>
       </c>
       <c r="J2" t="n">
+        <v>606</v>
+      </c>
+      <c r="K2" t="n">
         <v>603</v>
       </c>
-      <c r="K2" t="n">
-        <v>600</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.08839090320865406</v>
+        <v>0.0905386288457104</v>
       </c>
       <c r="M2" t="n">
-        <v>3.256229078951844</v>
+        <v>3.247047922707671</v>
       </c>
       <c r="N2" t="n">
-        <v>16.55102744412737</v>
+        <v>16.47893108175574</v>
       </c>
       <c r="O2" t="n">
-        <v>4.06829539784507</v>
+        <v>4.059424969346735</v>
       </c>
       <c r="P2" t="n">
-        <v>359.7084487276803</v>
+        <v>359.7263489403214</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31373,28 +31520,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.604901107699395</v>
+        <v>-6.566810070411597</v>
       </c>
       <c r="J3" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K3" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4892166744604319</v>
+        <v>0.4884520608415786</v>
       </c>
       <c r="M3" t="n">
-        <v>34.68542076466553</v>
+        <v>34.63698894378665</v>
       </c>
       <c r="N3" t="n">
-        <v>2053.560371815158</v>
+        <v>2049.086713239476</v>
       </c>
       <c r="O3" t="n">
-        <v>45.31622636335861</v>
+        <v>45.26683900207166</v>
       </c>
       <c r="P3" t="n">
-        <v>494.8370233851398</v>
+        <v>494.3693317328622</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31455,28 +31602,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008581409393957152</v>
+        <v>0.004666836364684212</v>
       </c>
       <c r="J4" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K4" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002250153760940954</v>
+        <v>6.702263210311976e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.943375245844183</v>
+        <v>2.945944080375343</v>
       </c>
       <c r="N4" t="n">
-        <v>15.05169430810345</v>
+        <v>15.0416224512547</v>
       </c>
       <c r="O4" t="n">
-        <v>3.879651312695955</v>
+        <v>3.878353059128926</v>
       </c>
       <c r="P4" t="n">
-        <v>365.2473663574006</v>
+        <v>365.2948533829632</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31537,28 +31684,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06143440755290709</v>
+        <v>-0.06248078436218357</v>
       </c>
       <c r="J5" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K5" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01678479251861353</v>
+        <v>0.01753526520486171</v>
       </c>
       <c r="M5" t="n">
-        <v>2.524304596465187</v>
+        <v>2.516945470325572</v>
       </c>
       <c r="N5" t="n">
-        <v>10.17030636516232</v>
+        <v>10.12506226404721</v>
       </c>
       <c r="O5" t="n">
-        <v>3.189091777475575</v>
+        <v>3.181990299175535</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1198588486968</v>
+        <v>368.1325495175041</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31615,28 +31762,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1036351329295182</v>
+        <v>-0.103750617952363</v>
       </c>
       <c r="J6" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K6" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03004151285767709</v>
+        <v>0.03043405723647274</v>
       </c>
       <c r="M6" t="n">
-        <v>3.124326341076079</v>
+        <v>3.110793981097648</v>
       </c>
       <c r="N6" t="n">
-        <v>15.95230491390648</v>
+        <v>15.8744617234756</v>
       </c>
       <c r="O6" t="n">
-        <v>3.994033664593537</v>
+        <v>3.984276813108697</v>
       </c>
       <c r="P6" t="n">
-        <v>364.3773543743302</v>
+        <v>364.3787495679169</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31693,28 +31840,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1686438717250598</v>
+        <v>-0.1727861085325044</v>
       </c>
       <c r="J7" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K7" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1204313448361967</v>
+        <v>0.1260702194360771</v>
       </c>
       <c r="M7" t="n">
-        <v>2.504912718504243</v>
+        <v>2.514165438011446</v>
       </c>
       <c r="N7" t="n">
-        <v>9.555411908419869</v>
+        <v>9.580359414089493</v>
       </c>
       <c r="O7" t="n">
-        <v>3.091182930274407</v>
+        <v>3.095215568274606</v>
       </c>
       <c r="P7" t="n">
-        <v>349.9988527913047</v>
+        <v>350.049101226219</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31775,28 +31922,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2332823606019113</v>
+        <v>-0.2328591341468275</v>
       </c>
       <c r="J8" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K8" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L8" t="n">
-        <v>0.185103339534706</v>
+        <v>0.1862308262494458</v>
       </c>
       <c r="M8" t="n">
-        <v>2.342238940014466</v>
+        <v>2.333057237061941</v>
       </c>
       <c r="N8" t="n">
-        <v>11.0212324727994</v>
+        <v>10.96822486911877</v>
       </c>
       <c r="O8" t="n">
-        <v>3.319824162933844</v>
+        <v>3.311831044772479</v>
       </c>
       <c r="P8" t="n">
-        <v>355.1216656234827</v>
+        <v>355.1165260332276</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31853,28 +32000,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1700566286171392</v>
+        <v>-0.1723946752011217</v>
       </c>
       <c r="J9" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K9" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08818459129385725</v>
+        <v>0.09118672035544861</v>
       </c>
       <c r="M9" t="n">
-        <v>2.687813294426141</v>
+        <v>2.686718636466077</v>
       </c>
       <c r="N9" t="n">
-        <v>13.75559647084552</v>
+        <v>13.71168691551663</v>
       </c>
       <c r="O9" t="n">
-        <v>3.708853794751893</v>
+        <v>3.702929504529709</v>
       </c>
       <c r="P9" t="n">
-        <v>361.8787118043097</v>
+        <v>361.9070717767045</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31931,28 +32078,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1170521165628195</v>
+        <v>-0.120270455487319</v>
       </c>
       <c r="J10" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="K10" t="n">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06374262618722881</v>
+        <v>0.06746840588207148</v>
       </c>
       <c r="M10" t="n">
-        <v>2.45501009291614</v>
+        <v>2.455963710393009</v>
       </c>
       <c r="N10" t="n">
-        <v>9.257674728094026</v>
+        <v>9.255100563226708</v>
       </c>
       <c r="O10" t="n">
-        <v>3.042642721072263</v>
+        <v>3.042219677016555</v>
       </c>
       <c r="P10" t="n">
-        <v>368.1416145968582</v>
+        <v>368.1806565276128</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31990,7 +32137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K604"/>
+  <dimension ref="A1:K607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66389,6 +66536,177 @@
         </is>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>-45.362287151004786,170.86234618593937</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>-45.362918021475494,170.86241912228974</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>-45.36351703795221,170.86244961938496</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>-45.36406291018568,170.86276188766783</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>-45.364654908026594,170.86302996728037</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>-45.36530046995244,170.86313965564432</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-45.36588496159714,170.86343929516352</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>-45.366392175546856,170.86388031391087</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>-45.36669783254145,170.86459608927885</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-45.36228654787524,170.86235712977262</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>-45.362918016036616,170.86241873943678</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>-45.36351606551434,170.8624652589917</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>-45.36406157696069,170.86276758113226</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>-45.364651852410155,170.86304129261444</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-45.36529703761031,170.86315551958663</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>-45.36588226950089,170.8634505355761</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>-45.36638450970686,170.86389433421567</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>-45.36669553592432,170.86459875956015</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>-45.36228633046783,170.8623610746427</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>-45.36291798159029,170.8624163147013</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>-45.363516120856374,170.86246436893282</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>-45.36406049903387,170.86277218435862</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>-45.3646516594238,170.86304200789866</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>-45.36529703761031,170.86315551958663</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>-45.365882761604574,170.8634484808771</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>-45.366386439954525,170.86389080392345</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>-45.3666912906622,170.8646036955341</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K607"/>
+  <dimension ref="A1:K609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24101,6 +24101,84 @@
         <v>362.56</v>
       </c>
       <c r="K607" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>354.2</v>
+      </c>
+      <c r="C608" t="n">
+        <v>351.37</v>
+      </c>
+      <c r="D608" t="n">
+        <v>362.05</v>
+      </c>
+      <c r="E608" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="F608" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="G608" t="n">
+        <v>342.41</v>
+      </c>
+      <c r="H608" t="n">
+        <v>349.59</v>
+      </c>
+      <c r="I608" t="n">
+        <v>355.37</v>
+      </c>
+      <c r="J608" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>354.78</v>
+      </c>
+      <c r="C609" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="D609" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="E609" t="n">
+        <v>366.06</v>
+      </c>
+      <c r="F609" t="n">
+        <v>361.94</v>
+      </c>
+      <c r="G609" t="n">
+        <v>343.11</v>
+      </c>
+      <c r="H609" t="n">
+        <v>349.32</v>
+      </c>
+      <c r="I609" t="n">
+        <v>354.55</v>
+      </c>
+      <c r="J609" t="n">
+        <v>362.25</v>
+      </c>
+      <c r="K609" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24117,7 +24195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B715"/>
+  <dimension ref="A1:B717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31270,6 +31348,26 @@
       </c>
       <c r="B715" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -31438,28 +31536,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1879042830050256</v>
+        <v>-0.1880287911702315</v>
       </c>
       <c r="J2" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K2" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0905386288457104</v>
+        <v>0.09126418738660613</v>
       </c>
       <c r="M2" t="n">
-        <v>3.247047922707671</v>
+        <v>3.237307222817366</v>
       </c>
       <c r="N2" t="n">
-        <v>16.47893108175574</v>
+        <v>16.42483732346157</v>
       </c>
       <c r="O2" t="n">
-        <v>4.059424969346735</v>
+        <v>4.052756756019483</v>
       </c>
       <c r="P2" t="n">
-        <v>359.7263489403214</v>
+        <v>359.7278618053688</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31520,28 +31618,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.566810070411597</v>
+        <v>-6.541554986133627</v>
       </c>
       <c r="J3" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K3" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4884520608415786</v>
+        <v>0.4879476655735073</v>
       </c>
       <c r="M3" t="n">
-        <v>34.63698894378665</v>
+        <v>34.60420434806926</v>
       </c>
       <c r="N3" t="n">
-        <v>2049.086713239476</v>
+        <v>2046.119632452425</v>
       </c>
       <c r="O3" t="n">
-        <v>45.26683900207166</v>
+        <v>45.23405390247954</v>
       </c>
       <c r="P3" t="n">
-        <v>494.3693317328622</v>
+        <v>494.0581849787114</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31602,28 +31700,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004666836364684212</v>
+        <v>0.002276358932630374</v>
       </c>
       <c r="J4" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K4" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L4" t="n">
-        <v>6.702263210311976e-05</v>
+        <v>1.602920608778646e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.945944080375343</v>
+        <v>2.946732667790327</v>
       </c>
       <c r="N4" t="n">
-        <v>15.0416224512547</v>
+        <v>15.02748258816917</v>
       </c>
       <c r="O4" t="n">
-        <v>3.878353059128926</v>
+        <v>3.876529709439767</v>
       </c>
       <c r="P4" t="n">
-        <v>365.2948533829632</v>
+        <v>365.3239557004902</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31684,28 +31782,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06248078436218357</v>
+        <v>-0.06274512583803364</v>
       </c>
       <c r="J5" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K5" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01753526520486171</v>
+        <v>0.01781120456725294</v>
       </c>
       <c r="M5" t="n">
-        <v>2.516945470325572</v>
+        <v>2.509947021628112</v>
       </c>
       <c r="N5" t="n">
-        <v>10.12506226404721</v>
+        <v>10.09218950050334</v>
       </c>
       <c r="O5" t="n">
-        <v>3.181990299175535</v>
+        <v>3.176820659165911</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1325495175041</v>
+        <v>368.1357679000884</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31762,28 +31860,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.103750617952363</v>
+        <v>-0.1035041138357398</v>
       </c>
       <c r="J6" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K6" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03043405723647274</v>
+        <v>0.03051420156625806</v>
       </c>
       <c r="M6" t="n">
-        <v>3.110793981097648</v>
+        <v>3.101787692188353</v>
       </c>
       <c r="N6" t="n">
-        <v>15.8744617234756</v>
+        <v>15.82261961139728</v>
       </c>
       <c r="O6" t="n">
-        <v>3.984276813108697</v>
+        <v>3.977765655666165</v>
       </c>
       <c r="P6" t="n">
-        <v>364.3787495679169</v>
+        <v>364.375748376183</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31840,28 +31938,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1727861085325044</v>
+        <v>-0.1746908505769061</v>
       </c>
       <c r="J7" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K7" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1260702194360771</v>
+        <v>0.1290786204818603</v>
       </c>
       <c r="M7" t="n">
-        <v>2.514165438011446</v>
+        <v>2.515741553600882</v>
       </c>
       <c r="N7" t="n">
-        <v>9.580359414089493</v>
+        <v>9.571691198334024</v>
       </c>
       <c r="O7" t="n">
-        <v>3.095215568274606</v>
+        <v>3.093814990967305</v>
       </c>
       <c r="P7" t="n">
-        <v>350.049101226219</v>
+        <v>350.072288026164</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31922,28 +32020,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2328591341468275</v>
+        <v>-0.232410153800373</v>
       </c>
       <c r="J8" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K8" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1862308262494458</v>
+        <v>0.186764070761547</v>
       </c>
       <c r="M8" t="n">
-        <v>2.333057237061941</v>
+        <v>2.327296739106817</v>
       </c>
       <c r="N8" t="n">
-        <v>10.96822486911877</v>
+        <v>10.93344805991513</v>
       </c>
       <c r="O8" t="n">
-        <v>3.311831044772479</v>
+        <v>3.306576486324659</v>
       </c>
       <c r="P8" t="n">
-        <v>355.1165260332276</v>
+        <v>355.1110608375174</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32000,28 +32098,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1723946752011217</v>
+        <v>-0.1740638785966444</v>
       </c>
       <c r="J9" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K9" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09118672035544861</v>
+        <v>0.09331938544855123</v>
       </c>
       <c r="M9" t="n">
-        <v>2.686718636466077</v>
+        <v>2.686540614300338</v>
       </c>
       <c r="N9" t="n">
-        <v>13.71168691551663</v>
+        <v>13.68432867869301</v>
       </c>
       <c r="O9" t="n">
-        <v>3.702929504529709</v>
+        <v>3.699233525839239</v>
       </c>
       <c r="P9" t="n">
-        <v>361.9070717767045</v>
+        <v>361.9273963432929</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32078,28 +32176,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.120270455487319</v>
+        <v>-0.1221421550227282</v>
       </c>
       <c r="J10" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K10" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06746840588207148</v>
+        <v>0.06977100656219282</v>
       </c>
       <c r="M10" t="n">
-        <v>2.455963710393009</v>
+        <v>2.455429408657863</v>
       </c>
       <c r="N10" t="n">
-        <v>9.255100563226708</v>
+        <v>9.246337958543398</v>
       </c>
       <c r="O10" t="n">
-        <v>3.042219677016555</v>
+        <v>3.040779169644418</v>
       </c>
       <c r="P10" t="n">
-        <v>368.1806565276128</v>
+        <v>368.2034442651299</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32137,7 +32235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K607"/>
+  <dimension ref="A1:K609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66707,6 +66805,120 @@
         </is>
       </c>
     </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>-45.36228607799453,170.86236565578213</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>-45.36291795076986,170.86241414520114</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>-45.3635162789765,170.86246182590736</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>-45.364059960070385,170.86277448597173</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-45.364651434273064,170.8630428423969</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-45.365296219128396,170.86315930252644</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-45.36588232739544,170.86345029384682</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>-45.36638655025438,170.86389060219244</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>-45.36669191701237,170.86460296727566</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-45.3622856712316,170.86237303650665</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-45.362917988842156,170.8624168251719</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-45.363516152480415,170.86246386032772</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-45.36406010190288,170.86277388028407</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-45.36465133777989,170.86304320003902</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>-45.36529437094296,170.86316784464822</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>-45.36588310897188,170.86344703050133</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>-45.36639107254842,170.86388233122113</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>-45.366693448090516,170.8646011870884</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K609"/>
+  <dimension ref="A1:K611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24179,6 +24179,84 @@
         <v>362.25</v>
       </c>
       <c r="K609" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>354.45</v>
+      </c>
+      <c r="C610" t="n">
+        <v>351.55</v>
+      </c>
+      <c r="D610" t="n">
+        <v>361.99</v>
+      </c>
+      <c r="E610" t="n">
+        <v>365.83</v>
+      </c>
+      <c r="F610" t="n">
+        <v>361.87</v>
+      </c>
+      <c r="G610" t="n">
+        <v>342.83</v>
+      </c>
+      <c r="H610" t="n">
+        <v>349.39</v>
+      </c>
+      <c r="I610" t="n">
+        <v>354.42</v>
+      </c>
+      <c r="J610" t="n">
+        <v>362.32</v>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>357.98</v>
+      </c>
+      <c r="C611" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="D611" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="E611" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="F611" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="G611" t="n">
+        <v>344.56</v>
+      </c>
+      <c r="H611" t="n">
+        <v>351.15</v>
+      </c>
+      <c r="I611" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="J611" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="K611" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24195,7 +24273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B717"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31368,6 +31446,36 @@
       </c>
       <c r="B717" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -31536,28 +31644,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1880287911702315</v>
+        <v>-0.1868871721820036</v>
       </c>
       <c r="J2" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K2" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09126418738660613</v>
+        <v>0.09078260349515299</v>
       </c>
       <c r="M2" t="n">
-        <v>3.237307222817366</v>
+        <v>3.232274418102376</v>
       </c>
       <c r="N2" t="n">
-        <v>16.42483732346157</v>
+        <v>16.38915035961631</v>
       </c>
       <c r="O2" t="n">
-        <v>4.052756756019483</v>
+        <v>4.048351560773385</v>
       </c>
       <c r="P2" t="n">
-        <v>359.7278618053688</v>
+        <v>359.7139139180713</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31618,28 +31726,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.541554986133627</v>
+        <v>-6.515756203064231</v>
       </c>
       <c r="J3" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K3" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4879476655735073</v>
+        <v>0.4873728308477622</v>
       </c>
       <c r="M3" t="n">
-        <v>34.60420434806926</v>
+        <v>34.57297522664562</v>
       </c>
       <c r="N3" t="n">
-        <v>2046.119632452425</v>
+        <v>2043.366815887026</v>
       </c>
       <c r="O3" t="n">
-        <v>45.23405390247954</v>
+        <v>45.20361507542318</v>
       </c>
       <c r="P3" t="n">
-        <v>494.0581849787114</v>
+        <v>493.739465307344</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31700,28 +31808,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002276358932630374</v>
+        <v>0.0007658314055338393</v>
       </c>
       <c r="J4" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K4" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L4" t="n">
-        <v>1.602920608778646e-05</v>
+        <v>1.825518852527352e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>2.946732667790327</v>
+        <v>2.943669916547482</v>
       </c>
       <c r="N4" t="n">
-        <v>15.02748258816917</v>
+        <v>14.9980203139561</v>
       </c>
       <c r="O4" t="n">
-        <v>3.876529709439767</v>
+        <v>3.872727761404887</v>
       </c>
       <c r="P4" t="n">
-        <v>365.3239557004902</v>
+        <v>365.3423827552124</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31782,28 +31890,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06274512583803364</v>
+        <v>-0.06201886465392951</v>
       </c>
       <c r="J5" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K5" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01781120456725294</v>
+        <v>0.01751713189703763</v>
       </c>
       <c r="M5" t="n">
-        <v>2.509947021628112</v>
+        <v>2.506761371273565</v>
       </c>
       <c r="N5" t="n">
-        <v>10.09218950050334</v>
+        <v>10.07080803328573</v>
       </c>
       <c r="O5" t="n">
-        <v>3.176820659165911</v>
+        <v>3.173453644420497</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1357679000884</v>
+        <v>368.1268847895078</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31860,28 +31968,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1035041138357398</v>
+        <v>-0.1027593286999207</v>
       </c>
       <c r="J6" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K6" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03051420156625806</v>
+        <v>0.03029974493688303</v>
       </c>
       <c r="M6" t="n">
-        <v>3.101787692188353</v>
+        <v>3.095299993487053</v>
       </c>
       <c r="N6" t="n">
-        <v>15.82261961139728</v>
+        <v>15.77595876823939</v>
       </c>
       <c r="O6" t="n">
-        <v>3.977765655666165</v>
+        <v>3.971896117503501</v>
       </c>
       <c r="P6" t="n">
-        <v>364.375748376183</v>
+        <v>364.3666482012794</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31938,28 +32046,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1746908505769061</v>
+        <v>-0.1758834061940762</v>
       </c>
       <c r="J7" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K7" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1290786204818603</v>
+        <v>0.1313343444709472</v>
       </c>
       <c r="M7" t="n">
-        <v>2.515741553600882</v>
+        <v>2.513616164438298</v>
       </c>
       <c r="N7" t="n">
-        <v>9.571691198334024</v>
+        <v>9.551658441837686</v>
       </c>
       <c r="O7" t="n">
-        <v>3.093814990967305</v>
+        <v>3.090575746012009</v>
       </c>
       <c r="P7" t="n">
-        <v>350.072288026164</v>
+        <v>350.086837774085</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32020,28 +32128,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.232410153800373</v>
+        <v>-0.2313628376600978</v>
       </c>
       <c r="J8" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K8" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L8" t="n">
-        <v>0.186764070761547</v>
+        <v>0.1864013656667763</v>
       </c>
       <c r="M8" t="n">
-        <v>2.327296739106817</v>
+        <v>2.32406885771233</v>
       </c>
       <c r="N8" t="n">
-        <v>10.93344805991513</v>
+        <v>10.90694275990449</v>
       </c>
       <c r="O8" t="n">
-        <v>3.306576486324659</v>
+        <v>3.30256608713656</v>
       </c>
       <c r="P8" t="n">
-        <v>355.1110608375174</v>
+        <v>355.0982658013763</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32098,28 +32206,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1740638785966444</v>
+        <v>-0.1753996928590428</v>
       </c>
       <c r="J9" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K9" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09331938544855123</v>
+        <v>0.09517649586187715</v>
       </c>
       <c r="M9" t="n">
-        <v>2.686540614300338</v>
+        <v>2.68460664311687</v>
       </c>
       <c r="N9" t="n">
-        <v>13.68432867869301</v>
+        <v>13.65357963627391</v>
       </c>
       <c r="O9" t="n">
-        <v>3.699233525839239</v>
+        <v>3.695075051507602</v>
       </c>
       <c r="P9" t="n">
-        <v>361.9273963432929</v>
+        <v>361.9436941162137</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32176,28 +32284,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1221421550227282</v>
+        <v>-0.1236066106040628</v>
       </c>
       <c r="J10" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K10" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06977100656219282</v>
+        <v>0.07172878550476036</v>
       </c>
       <c r="M10" t="n">
-        <v>2.455429408657863</v>
+        <v>2.453222308172589</v>
       </c>
       <c r="N10" t="n">
-        <v>9.246337958543398</v>
+        <v>9.230378496822041</v>
       </c>
       <c r="O10" t="n">
-        <v>3.040779169644418</v>
+        <v>3.038153797427319</v>
       </c>
       <c r="P10" t="n">
-        <v>368.2034442651299</v>
+        <v>368.2213166673166</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32235,7 +32343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K609"/>
+  <dimension ref="A1:K611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66919,6 +67027,120 @@
         </is>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-45.36228590266574,170.8623688371289</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>-45.36291798340326,170.86241644231893</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>-45.3635163264125,170.8624610629997</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>-45.364060754332336,170.8627710941208</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-45.36465156293064,170.86304236554076</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-45.36529511021722,170.86316442779957</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>-45.365882906340964,170.86344787655386</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>-45.36639178949741,170.86388101996945</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>-45.3666929609293,170.86460175351164</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:13+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-45.36228342701372,170.8624137577439</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-45.36291821546165,170.86243277737913</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-45.36351426294087,170.86249424948113</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-45.364051648680245,170.8628099792634</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-45.364646834763796,170.86305989000257</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-45.36529054255677,170.8631855390416</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-45.36587781161858,170.86346914873022</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>-45.366381311010514,170.8639001844137</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>-45.366685235943685,170.8646107353645</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
